--- a/web/public/forms/giseong-daebipyo.xlsx
+++ b/web/public/forms/giseong-daebipyo.xlsx
@@ -158,10 +158,10 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -173,10 +173,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -185,10 +185,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -599,7 +599,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="F1" s="26" t="inlineStr">

--- a/web/public/forms/giseong-daebipyo.xlsx
+++ b/web/public/forms/giseong-daebipyo.xlsx
@@ -594,7 +594,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
